--- a/results/link-prediction-gcn/Link/3shot/PTC_MR/GCN_total_results.xlsx
+++ b/results/link-prediction-gcn/Link/3shot/PTC_MR/GCN_total_results.xlsx
@@ -893,457 +893,457 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.4024±0.0000</t>
+          <t>0.4024±0.0006</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.5972±0.0015</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.5669±0.0000</t>
+          <t>0.5976±0.0016</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.5929±0.0000</t>
+          <t>0.5468±0.0361</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.5983±0.0000</t>
+          <t>0.5796±0.0185</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.5339±0.0000</t>
+          <t>0.5888±0.0098</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.5955±0.0000</t>
+          <t>0.5843±0.0224</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.5979±0.0000</t>
+          <t>0.5845±0.0095</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.5979±0.0000</t>
+          <t>0.5845±0.0095</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.5979±0.0000</t>
+          <t>0.5845±0.0095</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.5969±0.0000</t>
+          <t>0.6009±0.0274</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.5553±0.0000</t>
+          <t>0.5144±0.0145</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.6005±0.0000</t>
+          <t>0.5796±0.0273</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.4024±0.0000</t>
+          <t>0.4024±0.0006</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.5979±0.0003</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.5983±0.0015</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.5748±0.0000</t>
+          <t>0.4980±0.0579</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.5621±0.0391</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.5716±0.0000</t>
+          <t>0.5698±0.0146</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.5983±0.0015</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.5988±0.0012</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.5988±0.0012</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.5988±0.0012</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.5983±0.0015</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.6005±0.0000</t>
+          <t>0.5314±0.0494</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.5983±0.0015</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.4024±0.0000</t>
+          <t>0.4024±0.0006</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.5962±0.0000</t>
+          <t>0.5986±0.0018</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.5953±0.0000</t>
+          <t>0.5891±0.0101</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.5976±0.0022</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.5674±0.0397</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.5972±0.0000</t>
+          <t>0.5894±0.0306</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.5998±0.0000</t>
+          <t>0.5965±0.0003</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.5850±0.0000</t>
+          <t>0.5942±0.0036</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.5850±0.0000</t>
+          <t>0.5942±0.0036</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.5850±0.0000</t>
+          <t>0.5942±0.0036</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0.5998±0.0000</t>
+          <t>0.5974±0.0003</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.5254±0.0000</t>
+          <t>0.4625±0.0091</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.5993±0.0000</t>
+          <t>0.5931±0.0013</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>0.4024±0.0000</t>
+          <t>0.4024±0.0006</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>0.5414±0.0000</t>
+          <t>0.5831±0.0228</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.5811±0.0000</t>
+          <t>0.5818±0.0160</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.5645±0.0000</t>
+          <t>0.5422±0.0184</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.5873±0.0000</t>
+          <t>0.5872±0.0153</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.5586±0.0000</t>
+          <t>0.5890±0.0093</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>0.4982±0.0000</t>
+          <t>0.5573±0.0053</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.5230±0.0000</t>
+          <t>0.5199±0.0133</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.5230±0.0000</t>
+          <t>0.5199±0.0133</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>0.5230±0.0000</t>
+          <t>0.5199±0.0133</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>0.5268±0.0000</t>
+          <t>0.5619±0.0111</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.4959±0.0000</t>
+          <t>0.4764±0.0166</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.5360±0.0000</t>
+          <t>0.5417±0.0262</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.4024±0.0000</t>
+          <t>0.4024±0.0006</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>0.5962±0.0000</t>
+          <t>0.6036±0.0084</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>0.5998±0.0000</t>
+          <t>0.5937±0.0034</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0.5998±0.0000</t>
+          <t>0.5960±0.0023</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>0.5955±0.0000</t>
+          <t>0.5994±0.0014</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.5935±0.0074</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0.5998±0.0000</t>
+          <t>0.5969±0.0006</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.5957±0.0071</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.5957±0.0071</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.5957±0.0071</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.5998±0.0000</t>
+          <t>0.5728±0.0171</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.5645±0.0000</t>
+          <t>0.5540±0.0039</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.5972±0.0011</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>0.4024±0.0000</t>
+          <t>0.4024±0.0006</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>0.5998±0.0000</t>
+          <t>0.6012±0.0041</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>0.5991±0.0000</t>
+          <t>0.5809±0.0176</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.5962±0.0000</t>
+          <t>0.5755±0.0284</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.5521±0.0276</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.5950±0.0000</t>
+          <t>0.5991±0.0020</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.5998±0.0000</t>
+          <t>0.5969±0.0006</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>0.6005±0.0000</t>
+          <t>0.5894±0.0097</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>0.6005±0.0000</t>
+          <t>0.5894±0.0097</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>0.6005±0.0000</t>
+          <t>0.5894±0.0097</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>0.5991±0.0000</t>
+          <t>0.5969±0.0006</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>0.5373±0.0000</t>
+          <t>0.4929±0.0184</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>0.6005±0.0000</t>
+          <t>0.5961±0.0006</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>0.4024±0.0000</t>
+          <t>0.4024±0.0006</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>0.5047±0.0000</t>
+          <t>0.5274±0.0063</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>0.5077±0.0000</t>
+          <t>0.5252±0.0219</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.5101±0.0000</t>
+          <t>0.4996±0.0489</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.5386±0.0000</t>
+          <t>0.5613±0.0224</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0.6019±0.0000</t>
+          <t>0.5595±0.0371</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0.5112±0.0000</t>
+          <t>0.5246±0.0057</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.5178±0.0000</t>
+          <t>0.5206±0.0067</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.5178±0.0000</t>
+          <t>0.5206±0.0067</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.5178±0.0000</t>
+          <t>0.5206±0.0067</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>0.5184±0.0000</t>
+          <t>0.5142±0.0136</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>0.4756±0.0000</t>
+          <t>0.4862±0.0069</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>0.5407±0.0000</t>
+          <t>0.5205±0.0183</t>
         </is>
       </c>
     </row>
@@ -1360,62 +1360,62 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.7481±0.0000</t>
+          <t>0.7478±0.0011</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.7202±0.0000</t>
+          <t>0.7478±0.0014</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.7444±0.0000</t>
+          <t>0.6822±0.0561</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.7487±0.0000</t>
+          <t>0.7287±0.0212</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.6844±0.0000</t>
+          <t>0.7388±0.0106</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.7465±0.0000</t>
+          <t>0.7299±0.0285</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.7483±0.0000</t>
+          <t>0.7215±0.0252</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.7483±0.0000</t>
+          <t>0.7215±0.0252</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.7483±0.0000</t>
+          <t>0.7215±0.0252</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.7476±0.0000</t>
+          <t>0.7184±0.0370</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.6524±0.0000</t>
+          <t>0.6078±0.0150</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.7504±0.0000</t>
+          <t>0.7231±0.0286</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1425,62 +1425,62 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.7481±0.0000</t>
+          <t>0.7483±0.0003</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0.7481±0.0000</t>
+          <t>0.7487±0.0012</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.7296±0.0000</t>
+          <t>0.6518±0.0564</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.7481±0.0000</t>
+          <t>0.7122±0.0401</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.7249±0.0000</t>
+          <t>0.6972±0.0172</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0.7481±0.0000</t>
+          <t>0.7487±0.0012</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.7481±0.0000</t>
+          <t>0.7491±0.0009</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.7481±0.0000</t>
+          <t>0.7491±0.0009</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.7481±0.0000</t>
+          <t>0.7491±0.0009</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.7481±0.0000</t>
+          <t>0.7487±0.0012</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.7504±0.0000</t>
+          <t>0.6357±0.0835</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.7481±0.0000</t>
+          <t>0.7487±0.0012</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1490,62 +1490,62 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.7470±0.0000</t>
+          <t>0.7489±0.0014</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0.7459±0.0000</t>
+          <t>0.7395±0.0105</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>0.7481±0.0000</t>
+          <t>0.7480±0.0018</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.7481±0.0000</t>
+          <t>0.7177±0.0407</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.7478±0.0000</t>
+          <t>0.7284±0.0324</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.7498±0.0000</t>
+          <t>0.7472±0.0003</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.7374±0.0000</t>
+          <t>0.7433±0.0036</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.7374±0.0000</t>
+          <t>0.7433±0.0036</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.7374±0.0000</t>
+          <t>0.7433±0.0036</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>0.7498±0.0000</t>
+          <t>0.7478±0.0002</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>0.6249±0.0000</t>
+          <t>0.5638±0.0246</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.7494±0.0000</t>
+          <t>0.7422±0.0019</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1555,62 +1555,62 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>0.6761±0.0000</t>
+          <t>0.7348±0.0195</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.7334±0.0000</t>
+          <t>0.7343±0.0143</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.7178±0.0000</t>
+          <t>0.6752±0.0362</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.7388±0.0000</t>
+          <t>0.7299±0.0255</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.7115±0.0000</t>
+          <t>0.7389±0.0085</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>0.6239±0.0000</t>
+          <t>0.6944±0.0049</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.6462±0.0000</t>
+          <t>0.6669±0.0125</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0.6462±0.0000</t>
+          <t>0.6669±0.0125</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>0.6462±0.0000</t>
+          <t>0.6669±0.0125</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>0.6446±0.0000</t>
+          <t>0.7023±0.0101</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.6011±0.0000</t>
+          <t>0.5507±0.0207</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>0.6544±0.0000</t>
+          <t>0.6825±0.0240</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1620,62 +1620,62 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>0.7470±0.0000</t>
+          <t>0.7492±0.0018</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>0.7498±0.0000</t>
+          <t>0.7448±0.0029</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0.7498±0.0000</t>
+          <t>0.7466±0.0019</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>0.7465±0.0000</t>
+          <t>0.7493±0.0008</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>0.7481±0.0000</t>
+          <t>0.7434±0.0079</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>0.7498±0.0000</t>
+          <t>0.7476±0.0005</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>0.7481±0.0000</t>
+          <t>0.7453±0.0061</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>0.7481±0.0000</t>
+          <t>0.7453±0.0061</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>0.7481±0.0000</t>
+          <t>0.7453±0.0061</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.7498±0.0000</t>
+          <t>0.7173±0.0217</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.6892±0.0000</t>
+          <t>0.6795±0.0140</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>0.7481±0.0000</t>
+          <t>0.7478±0.0009</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
@@ -1685,62 +1685,62 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>0.7498±0.0000</t>
+          <t>0.7501±0.0020</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>0.7493±0.0000</t>
+          <t>0.7318±0.0172</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.7470±0.0000</t>
+          <t>0.7156±0.0437</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.7481±0.0000</t>
+          <t>0.6832±0.0241</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.7461±0.0000</t>
+          <t>0.7373±0.0153</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0.7498±0.0000</t>
+          <t>0.7476±0.0005</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>0.7504±0.0000</t>
+          <t>0.7382±0.0125</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>0.7504±0.0000</t>
+          <t>0.7382±0.0125</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>0.7504±0.0000</t>
+          <t>0.7382±0.0125</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>0.7493±0.0000</t>
+          <t>0.7476±0.0005</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>0.6603±0.0000</t>
+          <t>0.5687±0.0264</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>0.7504±0.0000</t>
+          <t>0.7469±0.0005</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
@@ -1750,62 +1750,62 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>0.6416±0.0000</t>
+          <t>0.6575±0.0108</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>0.6640±0.0000</t>
+          <t>0.6804±0.0234</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.6202±0.0000</t>
+          <t>0.6367±0.0605</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.6846±0.0000</t>
+          <t>0.7021±0.0257</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>0.7515±0.0000</t>
+          <t>0.7096±0.0378</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0.6462±0.0000</t>
+          <t>0.6571±0.0083</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.6548±0.0000</t>
+          <t>0.6553±0.0067</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.6548±0.0000</t>
+          <t>0.6553±0.0067</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>0.6548±0.0000</t>
+          <t>0.6553±0.0067</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>0.6553±0.0000</t>
+          <t>0.6528±0.0136</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>0.5859±0.0000</t>
+          <t>0.5674±0.0254</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>0.6689±0.0000</t>
+          <t>0.6576±0.0152</t>
         </is>
       </c>
     </row>
@@ -1817,457 +1817,457 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.6797±0.0000</t>
+          <t>0.4950±0.0636</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.6043±0.0000</t>
+          <t>0.5977±0.0114</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.4753±0.0000</t>
+          <t>0.4904±0.0018</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.4372±0.0000</t>
+          <t>0.6222±0.0864</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.5780±0.0000</t>
+          <t>0.5471±0.0493</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.4593±0.0000</t>
+          <t>0.4919±0.0160</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.5510±0.0000</t>
+          <t>0.5633±0.0227</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.5312±0.0000</t>
+          <t>0.5322±0.0206</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.5312±0.0000</t>
+          <t>0.5322±0.0206</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.5312±0.0000</t>
+          <t>0.5322±0.0206</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.4822±0.0000</t>
+          <t>0.5059±0.0144</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.5144±0.0000</t>
+          <t>0.4668±0.0100</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.5684±0.0000</t>
+          <t>0.5533±0.0334</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.6526±0.0000</t>
+          <t>0.6761±0.0377</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.5872±0.0000</t>
+          <t>0.5866±0.0239</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.4745±0.0000</t>
+          <t>0.4959±0.0037</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.3727±0.0000</t>
+          <t>0.4193±0.0761</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.5133±0.0000</t>
+          <t>0.5710±0.0533</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.5299±0.0000</t>
+          <t>0.5172±0.0095</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.5903±0.0000</t>
+          <t>0.5779±0.0044</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.6145±0.0000</t>
+          <t>0.5895±0.0082</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.6145±0.0000</t>
+          <t>0.5895±0.0082</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.6145±0.0000</t>
+          <t>0.5895±0.0082</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.5906±0.0000</t>
+          <t>0.5701±0.0172</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.4791±0.0000</t>
+          <t>0.4579±0.0156</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.6236±0.0000</t>
+          <t>0.5928±0.0058</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.7007±0.0000</t>
+          <t>0.6720±0.0255</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.5716±0.0000</t>
+          <t>0.5477±0.0405</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.4980±0.0000</t>
+          <t>0.5173±0.0294</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.4924±0.0043</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.5102±0.0000</t>
+          <t>0.5246±0.0418</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.5950±0.0000</t>
+          <t>0.5199±0.0379</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.5668±0.0000</t>
+          <t>0.5361±0.0316</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.5333±0.0000</t>
+          <t>0.5857±0.0281</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.5333±0.0000</t>
+          <t>0.5857±0.0281</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.5333±0.0000</t>
+          <t>0.5857±0.0281</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.5666±0.0000</t>
+          <t>0.5303±0.0039</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.4842±0.0000</t>
+          <t>0.4210±0.0160</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.5390±0.0000</t>
+          <t>0.5782±0.0154</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>0.6457±0.0000</t>
+          <t>0.5351±0.0804</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.4560±0.0000</t>
+          <t>0.5287±0.0323</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.4880±0.0000</t>
+          <t>0.4864±0.0119</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4753±0.0000</t>
+          <t>0.5361±0.0630</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.5074±0.0000</t>
+          <t>0.5281±0.0228</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.5399±0.0000</t>
+          <t>0.5252±0.0449</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.4601±0.0000</t>
+          <t>0.5141±0.0071</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.4735±0.0000</t>
+          <t>0.4722±0.0024</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.4735±0.0000</t>
+          <t>0.4722±0.0024</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.4735±0.0000</t>
+          <t>0.4722±0.0024</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.4667±0.0000</t>
+          <t>0.5333±0.0051</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.4665±0.0000</t>
+          <t>0.4482±0.0108</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.4953±0.0000</t>
+          <t>0.4976±0.0187</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.6598±0.0000</t>
+          <t>0.6412±0.0124</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0.5993±0.0000</t>
+          <t>0.5539±0.0302</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.4990±0.0000</t>
+          <t>0.5554±0.0907</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.4950±0.0000</t>
+          <t>0.6287±0.1163</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.5829±0.0000</t>
+          <t>0.5751±0.0387</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.5982±0.0000</t>
+          <t>0.5400±0.0224</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.5745±0.0000</t>
+          <t>0.5953±0.0095</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>0.5416±0.0000</t>
+          <t>0.5159±0.0166</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>0.5416±0.0000</t>
+          <t>0.5159±0.0166</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>0.5416±0.0000</t>
+          <t>0.5159±0.0166</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.5570±0.0000</t>
+          <t>0.5457±0.0207</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.5033±0.0000</t>
+          <t>0.4916±0.0108</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0.5632±0.0000</t>
+          <t>0.5805±0.0176</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>0.6213±0.0000</t>
+          <t>0.6677±0.0558</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.6102±0.0000</t>
+          <t>0.5697±0.0153</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.4954±0.0035</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.4881±0.0000</t>
+          <t>0.5129±0.0247</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.4568±0.0000</t>
+          <t>0.5423±0.0187</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.4980±0.0000</t>
+          <t>0.5362±0.0072</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.5840±0.0000</t>
+          <t>0.5643±0.0363</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0.5190±0.0000</t>
+          <t>0.5474±0.0123</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0.5190±0.0000</t>
+          <t>0.5474±0.0123</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>0.5190±0.0000</t>
+          <t>0.5474±0.0123</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.4954±0.0000</t>
+          <t>0.5672±0.0245</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.4938±0.0000</t>
+          <t>0.4799±0.0202</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>0.5251±0.0000</t>
+          <t>0.5549±0.0419</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>0.6631±0.0000</t>
+          <t>0.6119±0.0168</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.4620±0.0000</t>
+          <t>0.4883±0.0112</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0.4237±0.0000</t>
+          <t>0.4359±0.0177</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.4495±0.0000</t>
+          <t>0.4560±0.0771</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.5228±0.0000</t>
+          <t>0.5008±0.0602</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.5027±0.0000</t>
+          <t>0.5075±0.0358</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.4822±0.0000</t>
+          <t>0.4812±0.0149</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.4801±0.0000</t>
+          <t>0.4653±0.0121</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.4801±0.0000</t>
+          <t>0.4653±0.0121</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>0.4801±0.0000</t>
+          <t>0.4653±0.0121</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>0.4685±0.0000</t>
+          <t>0.4710±0.0253</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>0.4658±0.0000</t>
+          <t>0.4745±0.0083</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>0.5108±0.0000</t>
+          <t>0.4996±0.0275</t>
         </is>
       </c>
     </row>
@@ -2279,457 +2279,457 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.7383±0.0000</t>
+          <t>0.5732±0.0488</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.6447±0.0000</t>
+          <t>0.6611±0.0088</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.5856±0.0000</t>
+          <t>0.5937±0.0007</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.5668±0.0000</t>
+          <t>0.7359±0.0482</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.6473±0.0000</t>
+          <t>0.6425±0.0455</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.5751±0.0000</t>
+          <t>0.5730±0.0112</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.6541±0.0000</t>
+          <t>0.6498±0.0249</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.6086±0.0000</t>
+          <t>0.6083±0.0242</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.6086±0.0000</t>
+          <t>0.6083±0.0241</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.6086±0.0000</t>
+          <t>0.6083±0.0241</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.5619±0.0000</t>
+          <t>0.5891±0.0225</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.6095±0.0000</t>
+          <t>0.5665±0.0036</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.6333±0.0000</t>
+          <t>0.6453±0.0362</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.7251±0.0000</t>
+          <t>0.7357±0.0477</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.6369±0.0000</t>
+          <t>0.6491±0.0230</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.5851±0.0000</t>
+          <t>0.5964±0.0013</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.5352±0.0000</t>
+          <t>0.5753±0.0681</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.6201±0.0000</t>
+          <t>0.6604±0.0418</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.6354±0.0000</t>
+          <t>0.6042±0.0023</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.6432±0.0000</t>
+          <t>0.6481±0.0016</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.6652±0.0000</t>
+          <t>0.6507±0.0036</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6652±0.0000</t>
+          <t>0.6507±0.0036</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.6652±0.0000</t>
+          <t>0.6507±0.0036</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.6457±0.0000</t>
+          <t>0.6449±0.0114</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.6020±0.0000</t>
+          <t>0.5725±0.0075</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.6775±0.0000</t>
+          <t>0.6578±0.0041</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.7371±0.0000</t>
+          <t>0.7408±0.0212</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.6305±0.0000</t>
+          <t>0.6335±0.0291</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.5967±0.0000</t>
+          <t>0.6108±0.0189</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.5947±0.0035</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.6140±0.0000</t>
+          <t>0.6161±0.0285</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.6486±0.0000</t>
+          <t>0.5923±0.0195</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.6257±0.0000</t>
+          <t>0.5965±0.0323</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.6341±0.0000</t>
+          <t>0.6519±0.0215</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.6341±0.0000</t>
+          <t>0.6519±0.0215</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.6341±0.0000</t>
+          <t>0.6519±0.0215</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.6093±0.0000</t>
+          <t>0.5925±0.0061</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.5778±0.0000</t>
+          <t>0.5485±0.0074</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.6454±0.0000</t>
+          <t>0.6466±0.0199</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>0.7144±0.0000</t>
+          <t>0.6269±0.0744</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.5675±0.0000</t>
+          <t>0.6300±0.0215</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.5918±0.0000</t>
+          <t>0.5919±0.0067</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.5861±0.0000</t>
+          <t>0.6720±0.0597</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.5833±0.0000</t>
+          <t>0.6217±0.0213</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.6265±0.0000</t>
+          <t>0.6144±0.0225</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.5899±0.0000</t>
+          <t>0.6176±0.0087</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.5771±0.0000</t>
+          <t>0.5814±0.0084</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.5771±0.0000</t>
+          <t>0.5814±0.0084</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.5771±0.0000</t>
+          <t>0.5812±0.0084</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.5824±0.0000</t>
+          <t>0.6327±0.0059</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.5729±0.0000</t>
+          <t>0.5638±0.0185</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.5865±0.0000</t>
+          <t>0.6029±0.0155</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.7324±0.0000</t>
+          <t>0.7200±0.0292</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.6533±0.0000</t>
+          <t>0.6373±0.0479</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.5993±0.0000</t>
+          <t>0.6366±0.0615</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.5974±0.0000</t>
+          <t>0.7149±0.0828</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.6695±0.0000</t>
+          <t>0.6675±0.0505</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.6282±0.0000</t>
+          <t>0.6390±0.0364</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.6784±0.0000</t>
+          <t>0.6711±0.0103</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>0.6650±0.0000</t>
+          <t>0.5903±0.0235</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.6650±0.0000</t>
+          <t>0.5903±0.0235</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>0.6650±0.0000</t>
+          <t>0.5903±0.0235</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.6752±0.0000</t>
+          <t>0.6400±0.0287</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.5960±0.0000</t>
+          <t>0.5857±0.0021</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0.6574±0.0000</t>
+          <t>0.6616±0.0391</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.6966±0.0000</t>
+          <t>0.7386±0.0494</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>0.6815±0.0000</t>
+          <t>0.6425±0.0242</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0.5991±0.0000</t>
+          <t>0.6005±0.0108</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.5904±0.0000</t>
+          <t>0.6285±0.0472</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.5949±0.0000</t>
+          <t>0.6397±0.0098</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.5820±0.0000</t>
+          <t>0.6365±0.0070</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.6806±0.0000</t>
+          <t>0.6600±0.0187</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.5850±0.0000</t>
+          <t>0.6447±0.0162</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.5850±0.0000</t>
+          <t>0.6447±0.0162</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0.5849±0.0000</t>
+          <t>0.6447±0.0162</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.5778±0.0000</t>
+          <t>0.6427±0.0279</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.5939±0.0000</t>
+          <t>0.5854±0.0110</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>0.6192±0.0000</t>
+          <t>0.6349±0.0411</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>0.7442±0.0000</t>
+          <t>0.6862±0.0224</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.5771±0.0000</t>
+          <t>0.5962±0.0075</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.5601±0.0000</t>
+          <t>0.5666±0.0073</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.5730±0.0000</t>
+          <t>0.6002±0.0744</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.6245±0.0000</t>
+          <t>0.5991±0.0594</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.5825±0.0000</t>
+          <t>0.5927±0.0368</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.5859±0.0000</t>
+          <t>0.5939±0.0089</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.5764±0.0000</t>
+          <t>0.5810±0.0085</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.5764±0.0000</t>
+          <t>0.5809±0.0085</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.5764±0.0000</t>
+          <t>0.5810±0.0085</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>0.5817±0.0000</t>
+          <t>0.5868±0.0089</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>0.5986±0.0000</t>
+          <t>0.5810±0.0033</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>0.6066±0.0000</t>
+          <t>0.6044±0.0228</t>
         </is>
       </c>
     </row>
